--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/146.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/146.xlsx
@@ -426,13 +426,13 @@
         <v>-10.37510787417238</v>
       </c>
       <c r="E2">
-        <v>-19.02347981727932</v>
+        <v>-15.10200937795356</v>
       </c>
       <c r="F2">
-        <v>-4.345808551938567</v>
+        <v>-3.265015235586176</v>
       </c>
       <c r="G2">
-        <v>-11.89266554997597</v>
+        <v>-8.866291725329743</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.48587533217714</v>
       </c>
       <c r="E3">
-        <v>-17.92065684814097</v>
+        <v>-14.68539244353736</v>
       </c>
       <c r="F3">
-        <v>-3.967455882546906</v>
+        <v>-3.267819259244652</v>
       </c>
       <c r="G3">
-        <v>-11.37409335184314</v>
+        <v>-9.05203837075368</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-10.55377442217431</v>
       </c>
       <c r="E4">
-        <v>-19.4731313945732</v>
+        <v>-15.46374162471215</v>
       </c>
       <c r="F4">
-        <v>-4.084160424090315</v>
+        <v>-3.024261018738736</v>
       </c>
       <c r="G4">
-        <v>-12.04032012644327</v>
+        <v>-8.802408110557495</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.551101858572</v>
       </c>
       <c r="E5">
-        <v>-20.39456285909967</v>
+        <v>-15.69417009543629</v>
       </c>
       <c r="F5">
-        <v>-3.890991772696692</v>
+        <v>-3.07980802330086</v>
       </c>
       <c r="G5">
-        <v>-11.20852515136391</v>
+        <v>-9.0629317025601</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.48908591206972</v>
       </c>
       <c r="E6">
-        <v>-21.06786486623557</v>
+        <v>-16.76387535747045</v>
       </c>
       <c r="F6">
-        <v>-3.520256769941176</v>
+        <v>-3.165805813589893</v>
       </c>
       <c r="G6">
-        <v>-11.73324173689193</v>
+        <v>-8.902122889470476</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.36366357949943</v>
       </c>
       <c r="E7">
-        <v>-20.36732194602012</v>
+        <v>-17.05212898947018</v>
       </c>
       <c r="F7">
-        <v>-3.631643192758612</v>
+        <v>-2.97967911348747</v>
       </c>
       <c r="G7">
-        <v>-10.79105273214965</v>
+        <v>-9.130905048734325</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.18270646853431</v>
       </c>
       <c r="E8">
-        <v>-22.73862702441025</v>
+        <v>-18.1041623373172</v>
       </c>
       <c r="F8">
-        <v>-3.940049347025285</v>
+        <v>-2.756376941082209</v>
       </c>
       <c r="G8">
-        <v>-11.82812794368365</v>
+        <v>-8.915116565300448</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.942002057224467</v>
       </c>
       <c r="E9">
-        <v>-22.7766579805117</v>
+        <v>-18.58206405804257</v>
       </c>
       <c r="F9">
-        <v>-3.440370674349998</v>
+        <v>-2.604716951875468</v>
       </c>
       <c r="G9">
-        <v>-11.78233287281093</v>
+        <v>-8.825963553630816</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.649955289587307</v>
       </c>
       <c r="E10">
-        <v>-23.93488063551193</v>
+        <v>-18.74795993120152</v>
       </c>
       <c r="F10">
-        <v>-4.022396522170181</v>
+        <v>-2.564797098367157</v>
       </c>
       <c r="G10">
-        <v>-11.27828555221076</v>
+        <v>-8.935413799124058</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.307196079479654</v>
       </c>
       <c r="E11">
-        <v>-24.29545828952222</v>
+        <v>-19.96768333949981</v>
       </c>
       <c r="F11">
-        <v>-3.54250920348258</v>
+        <v>-2.35818155892389</v>
       </c>
       <c r="G11">
-        <v>-10.82989408480394</v>
+        <v>-8.70732479254915</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.932684468566224</v>
       </c>
       <c r="E12">
-        <v>-24.48532234523676</v>
+        <v>-20.2816744220795</v>
       </c>
       <c r="F12">
-        <v>-2.500796604459464</v>
+        <v>-2.370439739750517</v>
       </c>
       <c r="G12">
-        <v>-11.2137296707063</v>
+        <v>-8.553343076565289</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.542066054776983</v>
       </c>
       <c r="E13">
-        <v>-25.62472264651287</v>
+        <v>-21.0545538239395</v>
       </c>
       <c r="F13">
-        <v>-3.166003793399162</v>
+        <v>-2.005121431441907</v>
       </c>
       <c r="G13">
-        <v>-10.30855841352141</v>
+        <v>-8.497804706878537</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.169767351010972</v>
       </c>
       <c r="E14">
-        <v>-25.52735060700227</v>
+        <v>-21.2300768409494</v>
       </c>
       <c r="F14">
-        <v>-2.890008342134423</v>
+        <v>-1.881162876552184</v>
       </c>
       <c r="G14">
-        <v>-11.13160869959283</v>
+        <v>-8.01922911588156</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.842754366539116</v>
       </c>
       <c r="E15">
-        <v>-27.38267317002967</v>
+        <v>-23.10374413839857</v>
       </c>
       <c r="F15">
-        <v>-2.591236100762309</v>
+        <v>-1.704466310963229</v>
       </c>
       <c r="G15">
-        <v>-10.68711898997743</v>
+        <v>-8.04106538364163</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.594355762433134</v>
       </c>
       <c r="E16">
-        <v>-27.23861903522799</v>
+        <v>-22.81622562480334</v>
       </c>
       <c r="F16">
-        <v>-2.54225059439776</v>
+        <v>-1.25672296097386</v>
       </c>
       <c r="G16">
-        <v>-9.616455243906461</v>
+        <v>-7.34330734124233</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.444300781412802</v>
       </c>
       <c r="E17">
-        <v>-25.93338100575148</v>
+        <v>-23.70692747873739</v>
       </c>
       <c r="F17">
-        <v>-2.041605216963406</v>
+        <v>-0.8961056376761374</v>
       </c>
       <c r="G17">
-        <v>-9.410233834026718</v>
+        <v>-6.912709403596242</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.407721608483413</v>
       </c>
       <c r="E18">
-        <v>-28.15425469335066</v>
+        <v>-24.69355190142969</v>
       </c>
       <c r="F18">
-        <v>-2.364897133458386</v>
+        <v>-0.4854632069233524</v>
       </c>
       <c r="G18">
-        <v>-9.347254842255293</v>
+        <v>-6.779488328600913</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.486863633344522</v>
       </c>
       <c r="E19">
-        <v>-27.58634250018794</v>
+        <v>-25.4436343263277</v>
       </c>
       <c r="F19">
-        <v>-1.55412094082473</v>
+        <v>-0.2865282900388427</v>
       </c>
       <c r="G19">
-        <v>-8.088104474312015</v>
+        <v>-6.393484519315632</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.675568644152635</v>
       </c>
       <c r="E20">
-        <v>-29.97856938062689</v>
+        <v>-25.7203918693803</v>
       </c>
       <c r="F20">
-        <v>-1.521948807634803</v>
+        <v>-0.01774791885248716</v>
       </c>
       <c r="G20">
-        <v>-8.866871310628969</v>
+        <v>-6.000838975790558</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.961067199612834</v>
       </c>
       <c r="E21">
-        <v>-30.79025431250042</v>
+        <v>-26.59164423468018</v>
       </c>
       <c r="F21">
-        <v>-1.11704447788121</v>
+        <v>0.5781928445999219</v>
       </c>
       <c r="G21">
-        <v>-8.07219459677377</v>
+        <v>-5.370145740447775</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.320601946757812</v>
       </c>
       <c r="E22">
-        <v>-30.22695218390827</v>
+        <v>-27.04042363759585</v>
       </c>
       <c r="F22">
-        <v>-1.583282786872884</v>
+        <v>0.5817481974927374</v>
       </c>
       <c r="G22">
-        <v>-7.946790091084234</v>
+        <v>-6.069021181532072</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.730778078826726</v>
       </c>
       <c r="E23">
-        <v>-31.52581503400117</v>
+        <v>-28.28884988936004</v>
       </c>
       <c r="F23">
-        <v>-0.7184589346761722</v>
+        <v>0.6679315420799981</v>
       </c>
       <c r="G23">
-        <v>-8.229636854713153</v>
+        <v>-5.564158003247177</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.158575898610025</v>
       </c>
       <c r="E24">
-        <v>-31.78045257353773</v>
+        <v>-28.3427814150186</v>
       </c>
       <c r="F24">
-        <v>-0.6807930688708786</v>
+        <v>0.9547421581556876</v>
       </c>
       <c r="G24">
-        <v>-8.272201129154368</v>
+        <v>-5.552681170024643</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.577638078358399</v>
       </c>
       <c r="E25">
-        <v>-33.65244197361167</v>
+        <v>-28.05647356252456</v>
       </c>
       <c r="F25">
-        <v>-0.5744323510862277</v>
+        <v>0.8806894258150231</v>
       </c>
       <c r="G25">
-        <v>-8.84387978838733</v>
+        <v>-5.695405355331624</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.954833973996092</v>
       </c>
       <c r="E26">
-        <v>-31.06480650033954</v>
+        <v>-28.42687771452939</v>
       </c>
       <c r="F26">
-        <v>-1.118344186336203</v>
+        <v>0.9841674250379316</v>
       </c>
       <c r="G26">
-        <v>-8.336652580875182</v>
+        <v>-6.137276488122138</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.2700555252171</v>
       </c>
       <c r="E27">
-        <v>-33.56529721698846</v>
+        <v>-28.48525940612251</v>
       </c>
       <c r="F27">
-        <v>-0.6180409246392049</v>
+        <v>0.9302092291543774</v>
       </c>
       <c r="G27">
-        <v>-8.592937629034113</v>
+        <v>-6.126820456034729</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.49914945711931</v>
       </c>
       <c r="E28">
-        <v>-33.54303392768172</v>
+        <v>-28.86684192640811</v>
       </c>
       <c r="F28">
-        <v>-0.5106563447446938</v>
+        <v>0.5634628154433412</v>
       </c>
       <c r="G28">
-        <v>-8.316668636402506</v>
+        <v>-6.016537383016923</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.63234447220848</v>
       </c>
       <c r="E29">
-        <v>-33.00980520229264</v>
+        <v>-28.36008161679217</v>
       </c>
       <c r="F29">
-        <v>-0.8679519147571906</v>
+        <v>0.687032037653749</v>
       </c>
       <c r="G29">
-        <v>-7.93159425219166</v>
+        <v>-6.017247505545705</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.65928609849573</v>
       </c>
       <c r="E30">
-        <v>-32.09047733930221</v>
+        <v>-28.47890291618986</v>
       </c>
       <c r="F30">
-        <v>-0.4414752410998931</v>
+        <v>0.4584945832627962</v>
       </c>
       <c r="G30">
-        <v>-8.746646522208202</v>
+        <v>-6.021633556458776</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.58302702082215</v>
       </c>
       <c r="E31">
-        <v>-31.33252665554931</v>
+        <v>-28.04041309433144</v>
       </c>
       <c r="F31">
-        <v>-0.66568199070901</v>
+        <v>0.4420299527647532</v>
       </c>
       <c r="G31">
-        <v>-8.139662763869616</v>
+        <v>-6.288093981661571</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.40767811389786</v>
       </c>
       <c r="E32">
-        <v>-30.96808443840127</v>
+        <v>-27.99491051105662</v>
       </c>
       <c r="F32">
-        <v>-1.119667089078473</v>
+        <v>0.5343307906216882</v>
       </c>
       <c r="G32">
-        <v>-8.470645130897184</v>
+        <v>-6.143651926413637</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.14868025864801</v>
       </c>
       <c r="E33">
-        <v>-31.08252409985126</v>
+        <v>-27.96212506085843</v>
       </c>
       <c r="F33">
-        <v>-0.8077519704935421</v>
+        <v>0.3667669756485986</v>
       </c>
       <c r="G33">
-        <v>-8.763921819167599</v>
+        <v>-6.026027439605619</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.821433707468548</v>
       </c>
       <c r="E34">
-        <v>-30.88617065144168</v>
+        <v>-27.66774128894325</v>
       </c>
       <c r="F34">
-        <v>-0.8216668861257682</v>
+        <v>0.4231912212902869</v>
       </c>
       <c r="G34">
-        <v>-9.162602098815032</v>
+        <v>-6.124935498439946</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.449315473320516</v>
       </c>
       <c r="E35">
-        <v>-30.16315470474757</v>
+        <v>-26.96812868806456</v>
       </c>
       <c r="F35">
-        <v>-0.9889184065880023</v>
+        <v>0.2140284520834117</v>
       </c>
       <c r="G35">
-        <v>-8.762244415767809</v>
+        <v>-6.169840305407094</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.051486916107956</v>
       </c>
       <c r="E36">
-        <v>-30.23529598545985</v>
+        <v>-25.93879264010773</v>
       </c>
       <c r="F36">
-        <v>-1.376793159274843</v>
+        <v>-0.08499975481616782</v>
       </c>
       <c r="G36">
-        <v>-8.42552754824586</v>
+        <v>-5.856195893209109</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.651994943505098</v>
       </c>
       <c r="E37">
-        <v>-30.26278609121889</v>
+        <v>-26.28263285247896</v>
       </c>
       <c r="F37">
-        <v>-0.7259158980361733</v>
+        <v>0.309653528327781</v>
       </c>
       <c r="G37">
-        <v>-8.37981210508317</v>
+        <v>-5.656938644526161</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.267201996415096</v>
       </c>
       <c r="E38">
-        <v>-29.75060999403537</v>
+        <v>-26.00117802741798</v>
       </c>
       <c r="F38">
-        <v>-1.16047329570778</v>
+        <v>0.0007412415779978053</v>
       </c>
       <c r="G38">
-        <v>-8.213925393763832</v>
+        <v>-4.973641516417036</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.916944397578917</v>
       </c>
       <c r="E39">
-        <v>-28.26831225935876</v>
+        <v>-25.13595197175043</v>
       </c>
       <c r="F39">
-        <v>-1.645849376806331</v>
+        <v>-0.2475486335327092</v>
       </c>
       <c r="G39">
-        <v>-8.499265418477263</v>
+        <v>-5.666885581418303</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.6100803160651</v>
       </c>
       <c r="E40">
-        <v>-28.52101024920663</v>
+        <v>-25.23213619282213</v>
       </c>
       <c r="F40">
-        <v>-1.973351056442338</v>
+        <v>-0.003900929347290624</v>
       </c>
       <c r="G40">
-        <v>-8.194047184447095</v>
+        <v>-5.393613723577293</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.359602046577762</v>
       </c>
       <c r="E41">
-        <v>-27.48077617473345</v>
+        <v>-24.54286924135359</v>
       </c>
       <c r="F41">
-        <v>-1.272939909618466</v>
+        <v>0.005401636586147824</v>
       </c>
       <c r="G41">
-        <v>-8.790698921066353</v>
+        <v>-5.437737917911698</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.166482519743214</v>
       </c>
       <c r="E42">
-        <v>-28.93598043533254</v>
+        <v>-23.70210560038927</v>
       </c>
       <c r="F42">
-        <v>-0.7693911044372997</v>
+        <v>-0.09133842218238963</v>
       </c>
       <c r="G42">
-        <v>-7.765318539928246</v>
+        <v>-4.722224201548236</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.037491626990622</v>
       </c>
       <c r="E43">
-        <v>-27.0319344736479</v>
+        <v>-23.87028573977688</v>
       </c>
       <c r="F43">
-        <v>-0.8626089450091338</v>
+        <v>-0.1659983478293063</v>
       </c>
       <c r="G43">
-        <v>-7.706294826212356</v>
+        <v>-5.009962195168604</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.967098133591716</v>
       </c>
       <c r="E44">
-        <v>-25.64444209388316</v>
+        <v>-23.33600417531696</v>
       </c>
       <c r="F44">
-        <v>-1.190151214647878</v>
+        <v>-0.3432548897825529</v>
       </c>
       <c r="G44">
-        <v>-8.395845992989493</v>
+        <v>-4.750482901002446</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.956741626302159</v>
       </c>
       <c r="E45">
-        <v>-28.06706632800853</v>
+        <v>-22.80980891330648</v>
       </c>
       <c r="F45">
-        <v>-1.564735640724203</v>
+        <v>-0.09804819814506563</v>
       </c>
       <c r="G45">
-        <v>-7.963335684930415</v>
+        <v>-4.601218800494726</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.995974206767039</v>
       </c>
       <c r="E46">
-        <v>-25.83295635591713</v>
+        <v>-22.26716693444968</v>
       </c>
       <c r="F46">
-        <v>-1.482863120101111</v>
+        <v>-0.3959837884403526</v>
       </c>
       <c r="G46">
-        <v>-7.683465170135366</v>
+        <v>-4.650692410496323</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.082031358339143</v>
       </c>
       <c r="E47">
-        <v>-26.95688179179693</v>
+        <v>-22.12414279605656</v>
       </c>
       <c r="F47">
-        <v>-0.9125992610332783</v>
+        <v>-0.1321603677923493</v>
       </c>
       <c r="G47">
-        <v>-6.955517782656726</v>
+        <v>-4.306653709768596</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.202872977448101</v>
       </c>
       <c r="E48">
-        <v>-24.16024634163111</v>
+        <v>-21.63609478006464</v>
       </c>
       <c r="F48">
-        <v>-1.575165614692852</v>
+        <v>-0.4052233984511783</v>
       </c>
       <c r="G48">
-        <v>-7.012421571764632</v>
+        <v>-3.894618166165324</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.35308141248565</v>
       </c>
       <c r="E49">
-        <v>-25.50933812948649</v>
+        <v>-21.24405655026877</v>
       </c>
       <c r="F49">
-        <v>-1.643759405849067</v>
+        <v>-0.3106727147282399</v>
       </c>
       <c r="G49">
-        <v>-7.205619282251607</v>
+        <v>-3.950182643297988</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.522561433087695</v>
       </c>
       <c r="E50">
-        <v>-24.85365404479051</v>
+        <v>-20.47259754668187</v>
       </c>
       <c r="F50">
-        <v>-1.708956062286403</v>
+        <v>-0.5171888500831707</v>
       </c>
       <c r="G50">
-        <v>-7.164019677936807</v>
+        <v>-3.793848646437533</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.704718832588366</v>
       </c>
       <c r="E51">
-        <v>-23.84594376820206</v>
+        <v>-19.96258319599292</v>
       </c>
       <c r="F51">
-        <v>-2.048277716392956</v>
+        <v>-0.5979994036958737</v>
       </c>
       <c r="G51">
-        <v>-6.380167111156363</v>
+        <v>-3.67825270817681</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.891265999677356</v>
       </c>
       <c r="E52">
-        <v>-23.95695080049207</v>
+        <v>-20.49285275831306</v>
       </c>
       <c r="F52">
-        <v>-1.869673420675354</v>
+        <v>-0.4492279316226936</v>
       </c>
       <c r="G52">
-        <v>-7.711671654697755</v>
+        <v>-3.67583776943003</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.073786712224704</v>
       </c>
       <c r="E53">
-        <v>-23.20690160128466</v>
+        <v>-20.17166831371877</v>
       </c>
       <c r="F53">
-        <v>-2.231913515715161</v>
+        <v>-0.4317477226888185</v>
       </c>
       <c r="G53">
-        <v>-6.878874153695414</v>
+        <v>-3.724003396391479</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.244792127216765</v>
       </c>
       <c r="E54">
-        <v>-22.42627230709254</v>
+        <v>-19.76487787729711</v>
       </c>
       <c r="F54">
-        <v>-1.8582949660305</v>
+        <v>-0.7073886327051596</v>
       </c>
       <c r="G54">
-        <v>-7.100557698416026</v>
+        <v>-4.077461663603943</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.394686248636161</v>
       </c>
       <c r="E55">
-        <v>-23.97798681585233</v>
+        <v>-19.23242787903144</v>
       </c>
       <c r="F55">
-        <v>-1.30995799211477</v>
+        <v>-0.381257072753383</v>
       </c>
       <c r="G55">
-        <v>-7.859499845680362</v>
+        <v>-3.994661898896785</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.516675516954876</v>
       </c>
       <c r="E56">
-        <v>-22.12246074547001</v>
+        <v>-18.20073280704211</v>
       </c>
       <c r="F56">
-        <v>-1.71974968954488</v>
+        <v>-0.7063448897776322</v>
       </c>
       <c r="G56">
-        <v>-7.354909490205237</v>
+        <v>-4.13357178635615</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.601004139301685</v>
       </c>
       <c r="E57">
-        <v>-22.11932507091976</v>
+        <v>-18.25439229735889</v>
       </c>
       <c r="F57">
-        <v>-2.135420310432658</v>
+        <v>-0.6232496988680082</v>
       </c>
       <c r="G57">
-        <v>-8.32146457421638</v>
+        <v>-4.177176442516924</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.642630302127081</v>
       </c>
       <c r="E58">
-        <v>-23.042006652055</v>
+        <v>-18.47445435261626</v>
       </c>
       <c r="F58">
-        <v>-1.916298908309327</v>
+        <v>-0.8007025638957183</v>
       </c>
       <c r="G58">
-        <v>-8.309144470490917</v>
+        <v>-4.268393247785831</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.634551412860754</v>
       </c>
       <c r="E59">
-        <v>-21.4026386182847</v>
+        <v>-18.02305427335462</v>
       </c>
       <c r="F59">
-        <v>-2.220459679636653</v>
+        <v>-0.6647964659554174</v>
       </c>
       <c r="G59">
-        <v>-8.285818772941616</v>
+        <v>-4.135535066288667</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.57496840206769</v>
       </c>
       <c r="E60">
-        <v>-22.31419789949204</v>
+        <v>-17.94265225531726</v>
       </c>
       <c r="F60">
-        <v>-2.154439626000935</v>
+        <v>-0.4841328488744564</v>
       </c>
       <c r="G60">
-        <v>-9.206486104647055</v>
+        <v>-4.700492363571809</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.459804461584637</v>
       </c>
       <c r="E61">
-        <v>-21.61973112744481</v>
+        <v>-17.1859703776241</v>
       </c>
       <c r="F61">
-        <v>-1.948763455192443</v>
+        <v>-0.7681145902695857</v>
       </c>
       <c r="G61">
-        <v>-8.391082689483007</v>
+        <v>-4.870973985371505</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.2897157115484</v>
       </c>
       <c r="E62">
-        <v>-21.51236230827535</v>
+        <v>-17.10110365741255</v>
       </c>
       <c r="F62">
-        <v>-1.924961974607805</v>
+        <v>-0.5990663409106795</v>
       </c>
       <c r="G62">
-        <v>-8.406762821497233</v>
+        <v>-4.949479075226282</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.064901647830686</v>
       </c>
       <c r="E63">
-        <v>-21.43866357331626</v>
+        <v>-16.99156686193153</v>
       </c>
       <c r="F63">
-        <v>-1.972061288396179</v>
+        <v>-0.7851408538667267</v>
       </c>
       <c r="G63">
-        <v>-9.549376077754692</v>
+        <v>-5.615532235311104</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.789106862453083</v>
       </c>
       <c r="E64">
-        <v>-21.89346928586426</v>
+        <v>-16.60934682370756</v>
       </c>
       <c r="F64">
-        <v>-2.029013204073451</v>
+        <v>-0.7915457906251725</v>
       </c>
       <c r="G64">
-        <v>-8.905571683075337</v>
+        <v>-5.83251382902312</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.465632951878201</v>
       </c>
       <c r="E65">
-        <v>-21.40297918161334</v>
+        <v>-16.50507214697509</v>
       </c>
       <c r="F65">
-        <v>-2.003169797840911</v>
+        <v>-0.9676177671924159</v>
       </c>
       <c r="G65">
-        <v>-9.361392024216171</v>
+        <v>-5.771894950362061</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.100571352974507</v>
       </c>
       <c r="E66">
-        <v>-22.69339855308286</v>
+        <v>-17.14710462604636</v>
       </c>
       <c r="F66">
-        <v>-2.480765023924966</v>
+        <v>-0.7008644110407106</v>
       </c>
       <c r="G66">
-        <v>-9.214386217779763</v>
+        <v>-5.939084423232364</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.699722290990699</v>
       </c>
       <c r="E67">
-        <v>-19.06578858104535</v>
+        <v>-16.22800726628445</v>
       </c>
       <c r="F67">
-        <v>-2.43657659319003</v>
+        <v>-1.039051201805429</v>
       </c>
       <c r="G67">
-        <v>-9.056467498952504</v>
+        <v>-5.940157439259312</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.272783877783921</v>
       </c>
       <c r="E68">
-        <v>-19.94732845079683</v>
+        <v>-16.49063558440998</v>
       </c>
       <c r="F68">
-        <v>-2.331363164258256</v>
+        <v>-0.9929649813506779</v>
       </c>
       <c r="G68">
-        <v>-9.510180969208308</v>
+        <v>-6.708993003151672</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.829574992318166</v>
       </c>
       <c r="E69">
-        <v>-21.05394745508607</v>
+        <v>-15.57707445534407</v>
       </c>
       <c r="F69">
-        <v>-2.415530262587103</v>
+        <v>-1.125991674198848</v>
       </c>
       <c r="G69">
-        <v>-9.225967480785942</v>
+        <v>-5.961654310222539</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.384679852601344</v>
       </c>
       <c r="E70">
-        <v>-19.66258012915526</v>
+        <v>-16.46028391604814</v>
       </c>
       <c r="F70">
-        <v>-2.594506495268561</v>
+        <v>-1.140167525562956</v>
       </c>
       <c r="G70">
-        <v>-9.503813363150583</v>
+        <v>-6.318101879991826</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.949843380793332</v>
       </c>
       <c r="E71">
-        <v>-20.90440692812429</v>
+        <v>-15.89291371696331</v>
       </c>
       <c r="F71">
-        <v>-2.404995085958298</v>
+        <v>-1.386351690735746</v>
       </c>
       <c r="G71">
-        <v>-10.00789984491962</v>
+        <v>-6.232203161455018</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.540099040351325</v>
       </c>
       <c r="E72">
-        <v>-20.08987081667627</v>
+        <v>-16.09348475147326</v>
       </c>
       <c r="F72">
-        <v>-2.340536504876858</v>
+        <v>-0.9387367376938111</v>
       </c>
       <c r="G72">
-        <v>-9.325644403902352</v>
+        <v>-6.052445564123095</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.162726985712384</v>
       </c>
       <c r="E73">
-        <v>-20.80322639382882</v>
+        <v>-16.28945402783529</v>
       </c>
       <c r="F73">
-        <v>-2.878814613420393</v>
+        <v>-1.382716814572262</v>
       </c>
       <c r="G73">
-        <v>-9.415038909446661</v>
+        <v>-6.395225885957904</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.827165906368636</v>
       </c>
       <c r="E74">
-        <v>-20.78190380688715</v>
+        <v>-16.61153556607574</v>
       </c>
       <c r="F74">
-        <v>-2.201461901620849</v>
+        <v>-1.297707266594768</v>
       </c>
       <c r="G74">
-        <v>-9.757968043723166</v>
+        <v>-6.614016725671562</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.532435249355094</v>
       </c>
       <c r="E75">
-        <v>-21.22099792099332</v>
+        <v>-16.46113532436973</v>
       </c>
       <c r="F75">
-        <v>-3.302452471988297</v>
+        <v>-1.459712736295073</v>
       </c>
       <c r="G75">
-        <v>-8.525663962410306</v>
+        <v>-6.347981851837118</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.281292607213782</v>
       </c>
       <c r="E76">
-        <v>-20.94075583363919</v>
+        <v>-16.85003372640402</v>
       </c>
       <c r="F76">
-        <v>-2.842254618097837</v>
+        <v>-1.297695669451129</v>
       </c>
       <c r="G76">
-        <v>-8.792226206652154</v>
+        <v>-6.345749665211716</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.065533595044291</v>
       </c>
       <c r="E77">
-        <v>-21.39284119276943</v>
+        <v>-17.86085060506344</v>
       </c>
       <c r="F77">
-        <v>-2.8523930067407</v>
+        <v>-1.756138212815057</v>
       </c>
       <c r="G77">
-        <v>-9.72322686544922</v>
+        <v>-6.071261200391248</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.883516259247646</v>
       </c>
       <c r="E78">
-        <v>-20.43134369859235</v>
+        <v>-17.49963750972045</v>
       </c>
       <c r="F78">
-        <v>-2.931380323699841</v>
+        <v>-1.547364776287497</v>
       </c>
       <c r="G78">
-        <v>-8.619470626313596</v>
+        <v>-5.859973640632449</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.724257103416304</v>
       </c>
       <c r="E79">
-        <v>-21.43441483813096</v>
+        <v>-17.80525156505796</v>
       </c>
       <c r="F79">
-        <v>-2.985038650583582</v>
+        <v>-1.830697077638832</v>
       </c>
       <c r="G79">
-        <v>-9.263051802330411</v>
+        <v>-6.270171220043578</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.585132577700258</v>
       </c>
       <c r="E80">
-        <v>-21.15332549566657</v>
+        <v>-18.07310462303013</v>
       </c>
       <c r="F80">
-        <v>-3.528918179504848</v>
+        <v>-1.850904272062723</v>
       </c>
       <c r="G80">
-        <v>-9.081965336001611</v>
+        <v>-6.042952896789807</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.454657709872456</v>
       </c>
       <c r="E81">
-        <v>-21.6424118144897</v>
+        <v>-18.88359550664777</v>
       </c>
       <c r="F81">
-        <v>-2.863059893786549</v>
+        <v>-1.960488167411667</v>
       </c>
       <c r="G81">
-        <v>-9.093007480249724</v>
+        <v>-5.717518362018353</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.330012877671266</v>
       </c>
       <c r="E82">
-        <v>-23.4439378312266</v>
+        <v>-19.08521315041157</v>
       </c>
       <c r="F82">
-        <v>-3.582424915153876</v>
+        <v>-1.969026150232321</v>
       </c>
       <c r="G82">
-        <v>-8.304270210339308</v>
+        <v>-5.894837523902177</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.202269868088242</v>
       </c>
       <c r="E83">
-        <v>-24.62501976135869</v>
+        <v>-19.9542643137093</v>
       </c>
       <c r="F83">
-        <v>-3.843476618472113</v>
+        <v>-2.252688970177373</v>
       </c>
       <c r="G83">
-        <v>-8.828437234130895</v>
+        <v>-6.01338882504004</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.070573532836748</v>
       </c>
       <c r="E84">
-        <v>-24.55284525495582</v>
+        <v>-20.78027574804782</v>
       </c>
       <c r="F84">
-        <v>-3.624464560845952</v>
+        <v>-2.066383342715945</v>
       </c>
       <c r="G84">
-        <v>-8.11458134058279</v>
+        <v>-5.957304809733744</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.930718501519634</v>
       </c>
       <c r="E85">
-        <v>-25.60373646968851</v>
+        <v>-21.52910805633705</v>
       </c>
       <c r="F85">
-        <v>-3.103706422871626</v>
+        <v>-2.135800531070543</v>
       </c>
       <c r="G85">
-        <v>-7.927736877058289</v>
+        <v>-5.814651114530723</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.785428018089434</v>
       </c>
       <c r="E86">
-        <v>-25.75743851439777</v>
+        <v>-22.21145991094976</v>
       </c>
       <c r="F86">
-        <v>-3.524304173071255</v>
+        <v>-2.172472355992477</v>
       </c>
       <c r="G86">
-        <v>-8.870292691415624</v>
+        <v>-5.336146013637706</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.636287376831191</v>
       </c>
       <c r="E87">
-        <v>-27.53872593234878</v>
+        <v>-23.5167519321735</v>
       </c>
       <c r="F87">
-        <v>-3.15111057586423</v>
+        <v>-2.205499364342093</v>
       </c>
       <c r="G87">
-        <v>-9.764793835456631</v>
+        <v>-5.261956484592041</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.489688490075425</v>
       </c>
       <c r="E88">
-        <v>-28.10926918488578</v>
+        <v>-24.24414536360397</v>
       </c>
       <c r="F88">
-        <v>-3.342127128745379</v>
+        <v>-2.357392124789022</v>
       </c>
       <c r="G88">
-        <v>-9.236324304578888</v>
+        <v>-5.255857785227199</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.351990236772157</v>
       </c>
       <c r="E89">
-        <v>-27.98868900049203</v>
+        <v>-26.33974366140668</v>
       </c>
       <c r="F89">
-        <v>-3.553263897473125</v>
+        <v>-2.352509727316922</v>
       </c>
       <c r="G89">
-        <v>-8.369561016446164</v>
+        <v>-5.783259521567177</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.231927887768048</v>
       </c>
       <c r="E90">
-        <v>-30.43633217963817</v>
+        <v>-27.11117774572563</v>
       </c>
       <c r="F90">
-        <v>-3.726952661022515</v>
+        <v>-2.380685816155744</v>
       </c>
       <c r="G90">
-        <v>-8.878358586829869</v>
+        <v>-5.283654382888783</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.139589266346697</v>
       </c>
       <c r="E91">
-        <v>-32.06286056059776</v>
+        <v>-29.37624160182099</v>
       </c>
       <c r="F91">
-        <v>-3.391943487614936</v>
+        <v>-2.503305729322544</v>
       </c>
       <c r="G91">
-        <v>-8.858190584863518</v>
+        <v>-5.750606938966123</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.084053846958046</v>
       </c>
       <c r="E92">
-        <v>-33.63618838109196</v>
+        <v>-30.86513878929274</v>
       </c>
       <c r="F92">
-        <v>-3.851147300622036</v>
+        <v>-2.592723848617736</v>
       </c>
       <c r="G92">
-        <v>-8.52702285496998</v>
+        <v>-5.606574770618995</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.075695011609855</v>
       </c>
       <c r="E93">
-        <v>-34.82482084941259</v>
+        <v>-32.5297251222274</v>
       </c>
       <c r="F93">
-        <v>-3.851971526187822</v>
+        <v>-2.292472971431625</v>
       </c>
       <c r="G93">
-        <v>-9.24012815944814</v>
+        <v>-5.849394903549259</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.11948863712723</v>
       </c>
       <c r="E94">
-        <v>-36.4610718980836</v>
+        <v>-33.71287742820492</v>
       </c>
       <c r="F94">
-        <v>-3.458426598628818</v>
+        <v>-2.614007920665267</v>
       </c>
       <c r="G94">
-        <v>-8.513490060381944</v>
+        <v>-5.840445271090922</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.219402646407788</v>
       </c>
       <c r="E95">
-        <v>-37.68773116929436</v>
+        <v>-35.74410095047278</v>
       </c>
       <c r="F95">
-        <v>-3.647226440340076</v>
+        <v>-2.907804159048765</v>
       </c>
       <c r="G95">
-        <v>-9.110640449218105</v>
+        <v>-5.854107297536218</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.376381771574515</v>
       </c>
       <c r="E96">
-        <v>-40.26865089985425</v>
+        <v>-38.25911337051897</v>
       </c>
       <c r="F96">
-        <v>-3.923789323275733</v>
+        <v>-2.901073673901019</v>
       </c>
       <c r="G96">
-        <v>-9.666199065973238</v>
+        <v>-6.286007996733272</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.584237374234449</v>
       </c>
       <c r="E97">
-        <v>-40.26049399281229</v>
+        <v>-40.22397895884439</v>
       </c>
       <c r="F97">
-        <v>-3.665301417069161</v>
+        <v>-2.944648284390481</v>
       </c>
       <c r="G97">
-        <v>-9.975777243470565</v>
+        <v>-6.197955413908794</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.841941926450481</v>
       </c>
       <c r="E98">
-        <v>-43.39159378078354</v>
+        <v>-41.67510268931684</v>
       </c>
       <c r="F98">
-        <v>-4.012335171695778</v>
+        <v>-2.777594743737516</v>
       </c>
       <c r="G98">
-        <v>-9.741811450821061</v>
+        <v>-6.916836990794792</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.12787259166576</v>
       </c>
       <c r="E99">
-        <v>-45.95844969949472</v>
+        <v>-44.37032087214167</v>
       </c>
       <c r="F99">
-        <v>-4.405340003708155</v>
+        <v>-2.674568204749133</v>
       </c>
       <c r="G99">
-        <v>-9.824230046817917</v>
+        <v>-6.939707113412944</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.444931490622522</v>
       </c>
       <c r="E100">
-        <v>-47.24982119466047</v>
+        <v>-45.92645335944825</v>
       </c>
       <c r="F100">
-        <v>-3.912784462329542</v>
+        <v>-2.922085213073028</v>
       </c>
       <c r="G100">
-        <v>-9.838235386176944</v>
+        <v>-6.817534709527207</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.747083917803651</v>
       </c>
       <c r="E101">
-        <v>-49.80384161377227</v>
+        <v>-47.94024170057448</v>
       </c>
       <c r="F101">
-        <v>-3.9831070562554</v>
+        <v>-3.045442373228319</v>
       </c>
       <c r="G101">
-        <v>-10.20833976090234</v>
+        <v>-7.687641056108852</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.064423649089962</v>
       </c>
       <c r="E102">
-        <v>-50.42085203291428</v>
+        <v>-50.60276891875876</v>
       </c>
       <c r="F102">
-        <v>-4.256119556502658</v>
+        <v>-2.921208800360866</v>
       </c>
       <c r="G102">
-        <v>-10.50758722205264</v>
+        <v>-7.269407604846277</v>
       </c>
     </row>
   </sheetData>
